--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1648,6 +1648,78 @@
         <v>0</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SHIVAM TRADERS</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SHIVAM TRADERS</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>THE TOYS HOME</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>THE TOYS HOME</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MOHINI COLLECTION EXT</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MOHINI COLLECTION EXT</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1720,6 +1720,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S V GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>S V GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1744,6 +1744,54 @@
         <v>0</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SARDAR JI TOYS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SARDAR JI TOYS</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1768,30 +1768,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.5339</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,22 +907,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+          <t>R &amp; S ENTERPRISES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+          <t>R &amp; S ENTERPRISES</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -931,22 +931,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R &amp; S ENTERPRISES</t>
+          <t>ELARA AND COMPANY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R &amp; S ENTERPRISES</t>
+          <t>ELARA AND COMPANY</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.5238</v>
+        <v>0.4762</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5763</v>
+        <v>0.5339</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -955,22 +955,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ELARA AND COMPANY</t>
+          <t>SPILLBOX INNOVATION PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ELARA AND COMPANY</t>
+          <t>SPILLBOX INNOVATION PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -979,22 +979,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SPILLBOX INNOVATION PRIVATE LIMITED</t>
+          <t>MAA ENTERPRISES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SPILLBOX INNOVATION PRIVATE LIMITED</t>
+          <t>MAA ENTERPRISES</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.5238</v>
+        <v>0.4762</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5763</v>
+        <v>0.5339</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1003,12 +1003,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MAA ENTERPRISES</t>
+          <t>BANSAL BOOK AND STATIONERS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MAA ENTERPRISES</t>
+          <t>BANSAL BOOK AND STATIONERS</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1027,12 +1027,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BANSAL BOOK AND STATIONERS</t>
+          <t>TOYS TOWN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BANSAL BOOK AND STATIONERS</t>
+          <t>TOYS TOWN</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1051,12 +1051,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TOYS TOWN</t>
+          <t>SHREE BALAJI ENTERPRISES</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TOYS TOWN</t>
+          <t>SHREE BALAJI ENTERPRISES</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1075,12 +1075,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SHREE BALAJI ENTERPRISES</t>
+          <t>BABA SALES</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SHREE BALAJI ENTERPRISES</t>
+          <t>BABA SALES</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1099,12 +1099,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BABA SALES</t>
+          <t>EQUATOR TRADE HOUSE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BABA SALES</t>
+          <t>EQUATOR TRADE HOUSE</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1123,12 +1123,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EQUATOR TRADE HOUSE</t>
+          <t>THEME AMBIENCE ENTERPRISES PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EQUATOR TRADE HOUSE</t>
+          <t>THEME AMBIENCE ENTERPRISES PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1147,12 +1147,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>THEME AMBIENCE ENTERPRISES PRIVATE LIMITED</t>
+          <t>TEJAL INTERNATIONAL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>THEME AMBIENCE ENTERPRISES PRIVATE LIMITED</t>
+          <t>TEJAL INTERNATIONAL</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1171,12 +1171,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TEJAL INTERNATIONAL</t>
+          <t>MILLENNIUM INTERNATIONAL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TEJAL INTERNATIONAL</t>
+          <t>MILLENNIUM INTERNATIONAL</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1195,22 +1195,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MILLENNIUM INTERNATIONAL</t>
+          <t>SK ENTERPRISE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MILLENNIUM INTERNATIONAL</t>
+          <t>SK ENTERPRISE</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.4762</v>
+        <v>0.4972</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5339</v>
+        <v>0.5744</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1219,22 +1219,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SK ENTERPRISE</t>
+          <t>SHUBHAM ENTERPRISES</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SK ENTERPRISE</t>
+          <t>SHUBHAM ENTERPRISES</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.4972</v>
+        <v>0.4762</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5744</v>
+        <v>0.5339</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1243,22 +1243,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SHUBHAM ENTERPRISES</t>
+          <t>ANAND GIFT EMPORIUM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SHUBHAM ENTERPRISES</t>
+          <t>ANAND GIFT EMPORIUM</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1267,22 +1267,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ANAND GIFT EMPORIUM</t>
+          <t>RAJESH TRADERS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ANAND GIFT EMPORIUM</t>
+          <t>RAJESH TRADERS</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.5238</v>
+        <v>0.4762</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5763</v>
+        <v>0.5339</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1291,12 +1291,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RAJESH TRADERS</t>
+          <t>VIJAY SALES</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RAJESH TRADERS</t>
+          <t>VIJAY SALES</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1315,22 +1315,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VIJAY SALES</t>
+          <t>ZIPPYCUBS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VIJAY SALES</t>
+          <t>ZIPPYCUBS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1339,22 +1339,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ZIPPYCUBS PRIVATE LIMITED</t>
+          <t>SEEMA AND SONS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ZIPPYCUBS PRIVATE LIMITED</t>
+          <t>SEEMA AND SONS</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.5238</v>
+        <v>0.4738</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5763</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1363,22 +1363,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEEMA AND SONS</t>
+          <t>AGGARWAL MARKETING CO.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SEEMA AND SONS</t>
+          <t>AGGARWAL MARKETING CO.</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.4738</v>
+        <v>0.4308</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5072</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1387,22 +1387,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AGGARWAL MARKETING CO.</t>
+          <t>H S ENTERPRISES</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AGGARWAL MARKETING CO.</t>
+          <t>H S ENTERPRISES</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.4308</v>
+        <v>0.4762</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5072</v>
+        <v>0.5339</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1411,12 +1411,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>H S ENTERPRISES</t>
+          <t>MODERN AGENCIES</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H S ENTERPRISES</t>
+          <t>MODERN AGENCIES</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1435,12 +1435,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MODERN AGENCIES</t>
+          <t>PRINCE ENTERPRISES</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MODERN AGENCIES</t>
+          <t>PRINCE ENTERPRISES</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1459,22 +1459,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PRINCE ENTERPRISES</t>
+          <t>KIDS JUNCTION</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PRINCE ENTERPRISES</t>
+          <t>KIDS JUNCTION</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.4762</v>
+        <v>0.4286</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5339</v>
+        <v>0.4915</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KIDS JUNCTION</t>
+          <t>SATNAM MARKETING</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KIDS JUNCTION</t>
+          <t>SATNAM MARKETING</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4915</v>
+        <v>0.5339</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1507,22 +1507,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SATNAM MARKETING</t>
+          <t>Ramdev Extension</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SATNAM MARKETING</t>
+          <t>Ramdev Extension</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.4762</v>
+        <v>0.4286</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5339</v>
+        <v>0.4915</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1531,22 +1531,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ramdev Extension</t>
+          <t>T G ENTERPRISES</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ramdev Extension</t>
+          <t>T G ENTERPRISES</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4915</v>
+        <v>0.5339</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -1555,12 +1555,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>T G ENTERPRISES</t>
+          <t>RAMDEV IMPEX</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>T G ENTERPRISES</t>
+          <t>RAMDEV IMPEX</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1579,22 +1579,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RAMDEV IMPEX</t>
+          <t>CENTER ONE ENTERPRISES</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RAMDEV IMPEX</t>
+          <t>CENTER ONE ENTERPRISES</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1603,22 +1603,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CENTER ONE ENTERPRISES</t>
+          <t>BLISS ENTERPRISES</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CENTER ONE ENTERPRISES</t>
+          <t>BLISS ENTERPRISES</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.5238</v>
+        <v>0.4762</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5763</v>
+        <v>0.5339</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -1627,22 +1627,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BLISS ENTERPRISES</t>
+          <t>SHIVAM TRADERS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BLISS ENTERPRISES</t>
+          <t>SHIVAM TRADERS</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -1651,22 +1651,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SHIVAM TRADERS</t>
+          <t>THE TOYS HOME</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SHIVAM TRADERS</t>
+          <t>THE TOYS HOME</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.5238</v>
+        <v>0.4286</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5763</v>
+        <v>0.4915</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -1675,22 +1675,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>THE TOYS HOME</t>
+          <t>MOHINI COLLECTION EXT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>THE TOYS HOME</t>
+          <t>MOHINI COLLECTION EXT</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4915</v>
+        <v>0.5339</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -1699,12 +1699,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MOHINI COLLECTION EXT</t>
+          <t>S V GIFTS &amp; TOYS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MOHINI COLLECTION EXT</t>
+          <t>S V GIFTS &amp; TOYS</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1723,48 +1723,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S V GIFTS &amp; TOYS</t>
+          <t>SARDAR JI TOYS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S V GIFTS &amp; TOYS</t>
+          <t>SARDAR JI TOYS</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.4762</v>
+        <v>0.619</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.5339</v>
+        <v>0.661</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>SARDAR JI TOYS</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>SARDAR JI TOYS</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.661</v>
-      </c>
-      <c r="F56" t="n">
         <v>0</v>
       </c>
     </row>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1744,6 +1744,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1768,6 +1768,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>KASHMIR BOOK DEPOT</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KASHMIR BOOK DEPOT</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1768,30 +1768,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>KASHMIR BOOK DEPOT</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>KASHMIR BOOK DEPOT</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0.4286</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.4915</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1792,6 +1792,25 @@
         <v>0</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SAI TAK AND CO (BOSTON BOOKS, STATIONERY &amp; TOYS) REKHA REKHAJA (BOSTON BOOKS, STATIONERY &amp; TOYS)- MN CAPITAL 7-</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_discount_list.xlsx
+++ b/master_discount_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,6 +1798,11 @@
           <t>SAI TAK AND CO (BOSTON BOOKS, STATIONERY &amp; TOYS) REKHA REKHAJA (BOSTON BOOKS, STATIONERY &amp; TOYS)- MN CAPITAL 7-</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MAYA TOYS</t>
+        </is>
+      </c>
       <c r="C58" t="n">
         <v>0.4286</v>
       </c>
@@ -1808,6 +1813,54 @@
         <v>0.4915</v>
       </c>
       <c r="F58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>JAI BALAJI ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>JAI BALAJI ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>INTERVAL THE MAGIC LAMPS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>INTERVAL THE MAGIC LAMPS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F60" t="n">
         <v>0</v>
       </c>
     </row>
